--- a/docs/results/weekly-report/model.xlsx
+++ b/docs/results/weekly-report/model.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>rationale</t>
         </is>
       </c>
@@ -476,6 +481,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>[EST] One report a week, counted as four a month.</t>
         </is>
       </c>
@@ -496,6 +506,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>[EST] Time to gather numbers and write the report without an agent.</t>
         </is>
       </c>
@@ -516,6 +531,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>[EST] What you assume an hour of your own time is worth. Not a wage.</t>
         </is>
       </c>
@@ -536,6 +556,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>[EST] Share of hand-written reports you have to redo because a figure was wrong.</t>
         </is>
       </c>
@@ -556,6 +581,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>[EST] Residual mistakes you still expect after you read the draft.</t>
         </is>
       </c>
@@ -576,6 +606,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>[EST] Rework cost of one wrong report. Illustrative.</t>
         </is>
       </c>
@@ -596,6 +631,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>[EST] Notes pasted into a prompt. Not a measured trace.</t>
         </is>
       </c>
@@ -616,6 +656,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>[EST] Length of a draft report. Not a measured completion.</t>
         </is>
       </c>
@@ -636,6 +681,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>[EST] Illustrative blended price. Not a vendor price page.</t>
         </is>
       </c>
@@ -656,6 +706,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>[EST] Illustrative blended price. Not a vendor price page.</t>
         </is>
       </c>
@@ -676,6 +731,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>[EST] You still read the draft. If this reaches 90, the labor savings disappear.</t>
         </is>
       </c>
@@ -696,6 +756,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>[EST] In this personal example every report is reviewed. The low side is a sensitivity, not a policy.</t>
         </is>
       </c>
@@ -716,6 +781,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>[EST] An evening of setup, priced at the same assumed hourly rate. Not an invoice.</t>
         </is>
       </c>
@@ -736,6 +806,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>[EST] A slice of a personal subscription. Not a real plan price.</t>
         </is>
       </c>
@@ -756,6 +831,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>[EST] You either use it next month or you do not.</t>
         </is>
       </c>
@@ -776,6 +856,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>[EST] A personal discount rate for a 3-year sketch. Not a market rate.</t>
         </is>
       </c>
@@ -791,7 +876,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1 when the case is stated per month</t>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1 when the case is stated per month [EST]</t>
         </is>
       </c>
     </row>
@@ -806,6 +896,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>unused in this volume mode</t>
         </is>
       </c>
@@ -821,7 +916,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>unused in this volume mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Illustrative numbers, replace with your own</t>
         </is>
       </c>
     </row>
